--- a/data/trans_orig/IP07KS_C10_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C10_2023-Estudios-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de poder prestar atención en 2023 (tasa de respuesta: 99,83%)</t>
+          <t>Menores según la frecuencia de poder prestar atención, percibida por el/la menor en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5771</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2621</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9608</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>36,37%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>16,52%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>60,56%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7547</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4597</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10155</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>60,83%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>37,05%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>81,85%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>8635</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2316</t>
+          <t>5314</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9177</t>
+          <t>11615</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>13094</t>
+          <t>14406</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8486</t>
+          <t>8502</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18374</t>
+          <t>19262</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>64,6%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2961</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9768</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>37,82%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>18,66%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>61,56%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>4305</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1774</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7280</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>34,7%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>14,3%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>58,68%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>4719</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2899</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9786</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>10382</t>
+          <t>10719</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>6497</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15038</t>
+          <t>15846</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,15%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2583</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7130</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>16,28%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>44,94%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>555</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3745</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,47%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3107</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>4,27%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>30,18%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2769</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>8041</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>17,42%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>609</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10012</t>
+          <t>8731</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -1059,107 +1059,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>938</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4771</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,91%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>30,07%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>905</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4043</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,69%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>5447</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>3,14%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>25,44%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>905</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3734</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>3,2%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -1172,107 +1172,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>574</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2851</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3,62%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>17,97%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3702</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>3,75%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3310</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>23,29%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>2580</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>15866</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>15866</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>15866</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>12407</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>12407</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>12407</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15892</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15892</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15892</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>28299</t>
+          <t>29816</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>28299</t>
+          <t>29816</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>28299</t>
+          <t>29816</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>103026</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>87444</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>119771</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>51,43%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>43,65%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>59,79%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>67058</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>40002</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>84889</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>42,09%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>25,11%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>53,28%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>105656</t>
+          <t>69874</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>89173</t>
+          <t>59450</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>123376</t>
+          <t>80496</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>172714</t>
+          <t>172900</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>128896</t>
+          <t>153728</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>196453</t>
+          <t>194258</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>56,63%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>75091</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>60200</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>90698</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>37,48%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>30,05%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>45,27%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>85642</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>66207</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>115664</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>53,76%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>41,56%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>72,6%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>74461</t>
+          <t>65827</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58357</t>
+          <t>55528</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90239</t>
+          <t>76170</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>160103</t>
+          <t>140918</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>134070</t>
+          <t>120838</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>206915</t>
+          <t>159251</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>46,43%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>19658</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>12672</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>29909</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>9,81%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>6,33%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>14,93%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>5459</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2097</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>10818</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,43%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>6,79%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19933</t>
+          <t>5740</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12501</t>
+          <t>2764</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28494</t>
+          <t>10751</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>25392</t>
+          <t>25398</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16685</t>
+          <t>17375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>36152</t>
+          <t>35212</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2558</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8230</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1154</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5657</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1227</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7223</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2650</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9038</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>3786</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>900</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11011</t>
+          <t>9846</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>200333</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>200333</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>200333</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>159313</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>159313</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>159313</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>202700</t>
+          <t>142669</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>202700</t>
+          <t>142669</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>202700</t>
+          <t>142669</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>362013</t>
+          <t>343002</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>362013</t>
+          <t>343002</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>362013</t>
+          <t>343002</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>29885</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>23048</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>36275</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>56,38%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>43,48%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>68,44%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>22688</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>17627</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>27484</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>58,55%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>45,49%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>70,92%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>29734</t>
+          <t>23713</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23511</t>
+          <t>17650</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35833</t>
+          <t>28921</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>52422</t>
+          <t>53599</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43066</t>
+          <t>44382</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60034</t>
+          <t>61441</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,38%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>22237</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>15840</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>29104</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>41,95%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>29,88%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>54,91%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>15258</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>10536</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>20378</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>39,37%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>27,19%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>52,58%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22077</t>
+          <t>16411</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15617</t>
+          <t>11340</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28322</t>
+          <t>22477</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>37335</t>
+          <t>38648</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29670</t>
+          <t>30880</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>46355</t>
+          <t>47460</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,5%</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>881</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4463</t>
+          <t>4504</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>845</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4376</t>
+          <t>4472</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1688</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6030</t>
+          <t>5196</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>53004</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>53004</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>53004</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>38752</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>38752</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>38752</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>52693</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>52693</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>52693</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>91445</t>
+          <t>93974</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>91445</t>
+          <t>93974</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>91445</t>
+          <t>93974</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>138682</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>120430</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>157011</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>51,52%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>44,74%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>58,32%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>97293</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>61452</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>117701</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>46,23%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>29,2%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>55,92%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>140937</t>
+          <t>102223</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>121030</t>
+          <t>89629</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>161428</t>
+          <t>115935</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>238229</t>
+          <t>240905</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>196708</t>
+          <t>219774</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>264467</t>
+          <t>264584</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>56,68%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>103328</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>85591</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>121521</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>38,38%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>31,79%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>45,14%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>105205</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>84149</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>144460</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>49,99%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>39,98%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>68,64%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>102614</t>
+          <t>86957</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>83874</t>
+          <t>74334</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>121684</t>
+          <t>99397</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>207819</t>
+          <t>190285</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>182097</t>
+          <t>167962</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>256062</t>
+          <t>212585</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>45,54%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>23123</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>15647</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>34059</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>8,59%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>5,81%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>12,65%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>6820</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>3287</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>12548</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>23583</t>
+          <t>7181</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15416</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>34377</t>
+          <t>12519</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>30403</t>
+          <t>30304</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21512</t>
+          <t>21553</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>41381</t>
+          <t>41263</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>3496</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>11730</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>4,36%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>1154</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>6629</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1227</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>6241</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>3,15%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>3555</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>864</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>11452</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11747</t>
+          <t>12498</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -3218,107 +3218,107 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>574</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>3233</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>3253</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>2976</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>3253</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>269203</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>269203</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>269203</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>271285</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>271285</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>271285</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>481757</t>
+          <t>466791</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>481757</t>
+          <t>466791</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>481757</t>
+          <t>466791</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
